--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8687,0.0710,0.0077,0.0109</t>
-  </si>
-  <si>
-    <t>0.6416,0.0344,0.0128,0.2366</t>
-  </si>
-  <si>
-    <t>0.6869,0.0582,0.0205,0.1170</t>
-  </si>
-  <si>
-    <t>0.8702,0.0230,0.0067,0.0537</t>
-  </si>
-  <si>
-    <t>0.6765,0.1492,0.0104,0.0251</t>
-  </si>
-  <si>
-    <t>0.4336,0.2331,0.0056,0.0270</t>
-  </si>
-  <si>
-    <t>0.6623,0.1251,0.0122,0.0414</t>
-  </si>
-  <si>
-    <t>0.6333,0.2363,0.0148,0.0180</t>
-  </si>
-  <si>
-    <t>0.5793,0.2399,0.0141,0.0220</t>
-  </si>
-  <si>
-    <t>0.7178,0.0846,0.0062,0.0294</t>
-  </si>
-  <si>
-    <t>0.7243,0.1544,0.0102,0.0161</t>
-  </si>
-  <si>
-    <t>0.8464,0.0625,0.0044,0.0130</t>
-  </si>
-  <si>
-    <t>0.5129,0.3046,0.1285,0.0481</t>
-  </si>
-  <si>
-    <t>0.7731,0.0821,0.0671,0.0534</t>
-  </si>
-  <si>
-    <t>0.9124,0.0375,0.0146,0.0103</t>
-  </si>
-  <si>
-    <t>0.4608,0.0839,0.5104,0.0292</t>
-  </si>
-  <si>
-    <t>0.6826,0.1628,0.0328,0.0351</t>
-  </si>
-  <si>
-    <t>0.2697,0.6036,0.0665,0.0269</t>
-  </si>
-  <si>
-    <t>0.0358,0.9645,0.0172,0.0017</t>
-  </si>
-  <si>
-    <t>0.5943,0.2326,0.0136,0.0234</t>
-  </si>
-  <si>
-    <t>0.3456,0.6662,0.0296,0.0078</t>
-  </si>
-  <si>
-    <t>0.0895,0.9077,0.0365,0.0057</t>
-  </si>
-  <si>
-    <t>0.8481,0.0599,0.0410,0.0223</t>
-  </si>
-  <si>
-    <t>0.9236,0.0137,0.0154,0.0263</t>
-  </si>
-  <si>
-    <t>0.6367,0.1194,0.2333,0.0280</t>
-  </si>
-  <si>
-    <t>0.5706,0.2354,0.1493,0.0328</t>
-  </si>
-  <si>
-    <t>0.8023,0.0300,0.1542,0.0274</t>
-  </si>
-  <si>
-    <t>0.8694,0.0359,0.0473,0.0237</t>
-  </si>
-  <si>
-    <t>0.2067,0.2566,0.7012,0.0161</t>
-  </si>
-  <si>
-    <t>0.5935,0.2171,0.0129,0.0290</t>
-  </si>
-  <si>
-    <t>0.7077,0.1104,0.0428,0.0855</t>
-  </si>
-  <si>
-    <t>0.0216,0.8175,0.8472,0.0095</t>
-  </si>
-  <si>
-    <t>0.7089,0.0975,0.0534,0.0757</t>
-  </si>
-  <si>
-    <t>0.6909,0.0946,0.0119,0.0517</t>
-  </si>
-  <si>
-    <t>0.4940,0.1237,0.1359,0.2680</t>
-  </si>
-  <si>
-    <t>0.7160,0.1865,0.0208,0.0162</t>
-  </si>
-  <si>
-    <t>0.7168,0.1736,0.0085,0.0125</t>
-  </si>
-  <si>
-    <t>0.4399,0.2635,0.1149,0.0891</t>
-  </si>
-  <si>
-    <t>0.7228,0.0416,0.1670,0.0404</t>
-  </si>
-  <si>
-    <t>0.5520,0.1193,0.3337,0.0316</t>
-  </si>
-  <si>
-    <t>0.7196,0.1266,0.1415,0.0339</t>
-  </si>
-  <si>
-    <t>0.4273,0.0858,0.5025,0.0348</t>
-  </si>
-  <si>
-    <t>0.3068,0.7406,0.0335,0.0049</t>
-  </si>
-  <si>
-    <t>0.5574,0.1473,0.2783,0.0596</t>
-  </si>
-  <si>
-    <t>0.7226,0.1493,0.0230,0.0318</t>
-  </si>
-  <si>
-    <t>0.4569,0.3770,0.0128,0.0256</t>
-  </si>
-  <si>
-    <t>0.3284,0.7177,0.0268,0.0068</t>
-  </si>
-  <si>
-    <t>0.5423,0.4011,0.0148,0.0120</t>
-  </si>
-  <si>
-    <t>0.3511,0.1948,0.4524,0.0126</t>
-  </si>
-  <si>
-    <t>0.0495,0.7784,0.5638,0.0029</t>
-  </si>
-  <si>
-    <t>0.6869,0.1037,0.1887,0.0160</t>
-  </si>
-  <si>
-    <t>0.8588,0.0566,0.0470,0.0257</t>
-  </si>
-  <si>
-    <t>0.2940,0.4362,0.4515,0.0068</t>
-  </si>
-  <si>
-    <t>0.3648,0.4178,0.3354,0.0130</t>
-  </si>
-  <si>
-    <t>0.8452,0.0671,0.0047,0.0147</t>
-  </si>
-  <si>
-    <t>0.4584,0.3355,0.0191,0.0301</t>
-  </si>
-  <si>
-    <t>0.5876,0.3216,0.0178,0.0147</t>
-  </si>
-  <si>
-    <t>0.0183,0.8479,0.8569,0.0058</t>
-  </si>
-  <si>
-    <t>0.5752,0.1557,0.0202,0.0593</t>
-  </si>
-  <si>
-    <t>0.6547,0.1197,0.0220,0.0485</t>
-  </si>
-  <si>
-    <t>0.5275,0.4243,0.0115,0.0053</t>
-  </si>
-  <si>
-    <t>0.0325,0.9157,0.5534,0.0027</t>
-  </si>
-  <si>
-    <t>0.4330,0.1063,0.4691,0.0314</t>
-  </si>
-  <si>
-    <t>0.6442,0.0328,0.3316,0.0136</t>
-  </si>
-  <si>
-    <t>0.1067,0.8677,0.2105,0.0022</t>
-  </si>
-  <si>
-    <t>0.2237,0.1600,0.7530,0.0035</t>
-  </si>
-  <si>
-    <t>0.3970,0.6007,0.0886,0.0085</t>
-  </si>
-  <si>
-    <t>0.0193,0.9748,0.0414,0.0049</t>
-  </si>
-  <si>
-    <t>0.8576,0.0560,0.0145,0.0263</t>
-  </si>
-  <si>
-    <t>0.4803,0.2630,0.0734,0.0604</t>
-  </si>
-  <si>
-    <t>0.1833,0.7316,0.3509,0.0284</t>
-  </si>
-  <si>
-    <t>0.0513,0.8864,0.3432,0.0012</t>
-  </si>
-  <si>
-    <t>0.2837,0.7386,0.0723,0.0040</t>
-  </si>
-  <si>
-    <t>0.0288,0.9615,0.1663,0.0014</t>
-  </si>
-  <si>
-    <t>0.0149,0.9478,0.5174,0.0014</t>
-  </si>
-  <si>
-    <t>0.6984,0.0934,0.0469,0.1036</t>
-  </si>
-  <si>
-    <t>0.8400,0.0227,0.0019,0.0350</t>
-  </si>
-  <si>
-    <t>0.8616,0.0076,0.0019,0.0763</t>
-  </si>
-  <si>
-    <t>0.5978,0.0998,0.0408,0.1780</t>
-  </si>
-  <si>
-    <t>0.6459,0.1442,0.0439,0.0732</t>
-  </si>
-  <si>
-    <t>0.7616,0.0063,0.0054,0.2731</t>
-  </si>
-  <si>
-    <t>0.0664,0.8100,0.4831,0.0045</t>
-  </si>
-  <si>
-    <t>0.1459,0.6643,0.4563,0.0138</t>
-  </si>
-  <si>
-    <t>0.5275,0.3104,0.1821,0.0194</t>
-  </si>
-  <si>
-    <t>0.2580,0.3381,0.5192,0.0454</t>
-  </si>
-  <si>
-    <t>0.0278,0.8757,0.6658,0.0029</t>
-  </si>
-  <si>
-    <t>0.2901,0.6475,0.1587,0.0039</t>
-  </si>
-  <si>
-    <t>0.4919,0.2445,0.0185,0.0433</t>
-  </si>
-  <si>
-    <t>0.5801,0.1933,0.0212,0.0404</t>
-  </si>
-  <si>
-    <t>0.7358,0.1341,0.0077,0.0158</t>
-  </si>
-  <si>
-    <t>0.4471,0.4231,0.0409,0.0255</t>
-  </si>
-  <si>
-    <t>0.5934,0.2315,0.0228,0.0255</t>
-  </si>
-  <si>
-    <t>0.7264,0.1081,0.0140,0.0349</t>
-  </si>
-  <si>
-    <t>0.5842,0.1705,0.0170,0.0553</t>
-  </si>
-  <si>
-    <t>0.7251,0.1177,0.0097,0.0273</t>
-  </si>
-  <si>
-    <t>0.6392,0.1876,0.0215,0.0389</t>
-  </si>
-  <si>
-    <t>0.4804,0.4097,0.0290,0.0204</t>
-  </si>
-  <si>
-    <t>0.7621,0.1184,0.0105,0.0179</t>
-  </si>
-  <si>
-    <t>0.7244,0.1012,0.0118,0.0308</t>
-  </si>
-  <si>
-    <t>0.3778,0.4946,0.0353,0.0321</t>
-  </si>
-  <si>
-    <t>0.6396,0.3628,0.0154,0.0065</t>
-  </si>
-  <si>
-    <t>0.5836,0.3636,0.0159,0.0080</t>
-  </si>
-  <si>
-    <t>0.7360,0.1847,0.0138,0.0125</t>
-  </si>
-  <si>
-    <t>0.0534,0.4863,0.8944,0.0090</t>
-  </si>
-  <si>
-    <t>0.6932,0.1046,0.0730,0.1028</t>
-  </si>
-  <si>
-    <t>0.9297,0.0148,0.0319,0.0134</t>
-  </si>
-  <si>
-    <t>0.8224,0.0417,0.0904,0.0268</t>
-  </si>
-  <si>
-    <t>0.0903,0.7887,0.0943,0.0520</t>
-  </si>
-  <si>
-    <t>0.0151,0.9686,0.0566,0.0081</t>
-  </si>
-  <si>
-    <t>0.3143,0.6125,0.0296,0.0156</t>
-  </si>
-  <si>
-    <t>0.4816,0.4794,0.0400,0.0101</t>
-  </si>
-  <si>
-    <t>0.1339,0.8106,0.0500,0.0127</t>
-  </si>
-  <si>
-    <t>0.0402,0.9372,0.0066,0.0093</t>
-  </si>
-  <si>
-    <t>0.4523,0.4762,0.0053,0.0063</t>
-  </si>
-  <si>
-    <t>0.9069,0.0097,0.0020,0.0324</t>
-  </si>
-  <si>
-    <t>0.6997,0.1533,0.0873,0.0570</t>
-  </si>
-  <si>
-    <t>0.9119,0.0253,0.0136,0.0133</t>
-  </si>
-  <si>
-    <t>0.8573,0.0404,0.0241,0.0280</t>
-  </si>
-  <si>
-    <t>0.6452,0.0765,0.0253,0.1210</t>
-  </si>
-  <si>
-    <t>0.3212,0.5645,0.0915,0.0279</t>
-  </si>
-  <si>
-    <t>0.5715,0.4251,0.0116,0.0074</t>
-  </si>
-  <si>
-    <t>0.1246,0.8180,0.0327,0.0113</t>
-  </si>
-  <si>
-    <t>0.0680,0.9382,0.1247,0.0022</t>
-  </si>
-  <si>
-    <t>0.4868,0.4973,0.0320,0.0091</t>
-  </si>
-  <si>
-    <t>0.4708,0.2417,0.0171,0.0522</t>
-  </si>
-  <si>
-    <t>0.6440,0.2229,0.0167,0.0225</t>
-  </si>
-  <si>
-    <t>0.6945,0.1984,0.0156,0.0155</t>
-  </si>
-  <si>
-    <t>0.6919,0.2044,0.0165,0.0153</t>
-  </si>
-  <si>
-    <t>0.5734,0.1792,0.0157,0.0403</t>
-  </si>
-  <si>
-    <t>0.3734,0.4638,0.0367,0.0294</t>
-  </si>
-  <si>
-    <t>0.7944,0.0546,0.0139,0.0469</t>
-  </si>
-  <si>
-    <t>0.8111,0.0978,0.0067,0.0129</t>
-  </si>
-  <si>
-    <t>0.8019,0.0879,0.0136,0.0290</t>
-  </si>
-  <si>
-    <t>0.7690,0.0784,0.0109,0.0411</t>
-  </si>
-  <si>
-    <t>0.3174,0.1651,0.5162,0.0092</t>
-  </si>
-  <si>
-    <t>0.7559,0.1174,0.1045,0.0046</t>
-  </si>
-  <si>
-    <t>0.2851,0.3279,0.5297,0.0241</t>
-  </si>
-  <si>
-    <t>0.5619,0.1740,0.2811,0.0518</t>
-  </si>
-  <si>
-    <t>0.7893,0.0813,0.0138,0.0266</t>
-  </si>
-  <si>
-    <t>0.6658,0.2422,0.0221,0.0172</t>
-  </si>
-  <si>
-    <t>0.9026,0.0320,0.0112,0.0223</t>
-  </si>
-  <si>
-    <t>0.8679,0.0260,0.0098,0.0445</t>
-  </si>
-  <si>
-    <t>0.8255,0.0483,0.0299,0.0528</t>
-  </si>
-  <si>
-    <t>0.4979,0.0206,0.0053,0.4260</t>
-  </si>
-  <si>
-    <t>0.9057,0.0153,0.0078,0.0423</t>
-  </si>
-  <si>
-    <t>0.7131,0.0484,0.0268,0.1324</t>
-  </si>
-  <si>
-    <t>0.0091,0.9653,0.4151,0.0111</t>
-  </si>
-  <si>
-    <t>0.7416,0.1036,0.0128,0.0363</t>
-  </si>
-  <si>
-    <t>0.2800,0.6647,0.0351,0.0114</t>
-  </si>
-  <si>
-    <t>0.6838,0.2390,0.0142,0.0135</t>
-  </si>
-  <si>
-    <t>0.5951,0.1971,0.0146,0.0305</t>
-  </si>
-  <si>
-    <t>0.7900,0.0625,0.0164,0.0543</t>
-  </si>
-  <si>
-    <t>0.8850,0.0130,0.0018,0.0389</t>
-  </si>
-  <si>
-    <t>0.7822,0.0377,0.0066,0.0547</t>
-  </si>
-  <si>
-    <t>0.0352,0.7964,0.7811,0.0168</t>
-  </si>
-  <si>
-    <t>0.8766,0.0415,0.0027,0.0116</t>
-  </si>
-  <si>
-    <t>0.5398,0.3268,0.0270,0.0263</t>
-  </si>
-  <si>
-    <t>0.7761,0.1505,0.0099,0.0143</t>
-  </si>
-  <si>
-    <t>0.6798,0.2294,0.0668,0.0250</t>
-  </si>
-  <si>
-    <t>0.7853,0.1769,0.0099,0.0064</t>
-  </si>
-  <si>
-    <t>0.7400,0.0698,0.0091,0.0456</t>
-  </si>
-  <si>
-    <t>0.6425,0.2383,0.0269,0.0224</t>
-  </si>
-  <si>
-    <t>0.7280,0.1340,0.0289,0.0325</t>
-  </si>
-  <si>
-    <t>0.6251,0.1978,0.0243,0.0360</t>
-  </si>
-  <si>
-    <t>0.7451,0.1460,0.0137,0.0187</t>
-  </si>
-  <si>
-    <t>0.7460,0.2124,0.0084,0.0082</t>
-  </si>
-  <si>
-    <t>0.7171,0.1296,0.0117,0.0242</t>
-  </si>
-  <si>
-    <t>0.6650,0.2377,0.0144,0.0150</t>
-  </si>
-  <si>
-    <t>0.4821,0.3079,0.0579,0.0485</t>
-  </si>
-  <si>
-    <t>0.6654,0.1664,0.0063,0.0197</t>
-  </si>
-  <si>
-    <t>0.7093,0.1309,0.0107,0.0234</t>
-  </si>
-  <si>
-    <t>0.2720,0.5961,0.0507,0.0270</t>
-  </si>
-  <si>
-    <t>0.6321,0.2138,0.0377,0.0289</t>
-  </si>
-  <si>
-    <t>0.6535,0.1211,0.0111,0.0538</t>
-  </si>
-  <si>
-    <t>0.5175,0.2107,0.0263,0.0682</t>
-  </si>
-  <si>
-    <t>0.4492,0.3911,0.0459,0.0409</t>
-  </si>
-  <si>
-    <t>0.5697,0.1215,0.0215,0.1076</t>
-  </si>
-  <si>
-    <t>0.6133,0.1572,0.0042,0.0174</t>
-  </si>
-  <si>
-    <t>0.5811,0.2356,0.0209,0.0295</t>
-  </si>
-  <si>
-    <t>0.0153,0.7396,0.9225,0.0028</t>
-  </si>
-  <si>
-    <t>0.6930,0.1102,0.0140,0.0446</t>
-  </si>
-  <si>
-    <t>0.1426,0.1559,0.8226,0.0030</t>
-  </si>
-  <si>
-    <t>0.4413,0.2230,0.3042,0.0530</t>
-  </si>
-  <si>
-    <t>0.4280,0.3333,0.2514,0.0371</t>
-  </si>
-  <si>
-    <t>0.5079,0.1759,0.2391,0.1091</t>
-  </si>
-  <si>
-    <t>0.7014,0.0548,0.2010,0.0482</t>
-  </si>
-  <si>
-    <t>0.4393,0.0414,0.6453,0.0066</t>
-  </si>
-  <si>
-    <t>0.6888,0.0488,0.2736,0.0233</t>
-  </si>
-  <si>
-    <t>0.6126,0.2239,0.0853,0.0413</t>
-  </si>
-  <si>
-    <t>0.7963,0.0994,0.0491,0.0287</t>
-  </si>
-  <si>
-    <t>0.7122,0.1733,0.0357,0.0330</t>
-  </si>
-  <si>
-    <t>0.6964,0.1274,0.0776,0.0530</t>
-  </si>
-  <si>
-    <t>0.6430,0.2557,0.0945,0.0385</t>
-  </si>
-  <si>
-    <t>0.6647,0.1311,0.1388,0.0726</t>
-  </si>
-  <si>
-    <t>0.7927,0.0606,0.0243,0.0710</t>
-  </si>
-  <si>
-    <t>0.5814,0.2586,0.0697,0.0468</t>
-  </si>
-  <si>
-    <t>0.6325,0.2261,0.0198,0.0224</t>
-  </si>
-  <si>
-    <t>0.8719,0.0510,0.0048,0.0127</t>
-  </si>
-  <si>
-    <t>0.6793,0.1677,0.0184,0.0283</t>
-  </si>
-  <si>
-    <t>0.7956,0.1217,0.0088,0.0121</t>
-  </si>
-  <si>
-    <t>0.3693,0.4855,0.0818,0.0462</t>
-  </si>
-  <si>
-    <t>0.8778,0.0502,0.0080,0.0131</t>
-  </si>
-  <si>
-    <t>0.8993,0.0179,0.0043,0.0241</t>
-  </si>
-  <si>
-    <t>0.8596,0.0448,0.0301,0.0272</t>
-  </si>
-  <si>
-    <t>0.8371,0.0675,0.0215,0.0230</t>
-  </si>
-  <si>
-    <t>0.5642,0.1691,0.0401,0.0849</t>
-  </si>
-  <si>
-    <t>0.7168,0.1706,0.0650,0.0145</t>
-  </si>
-  <si>
-    <t>0.7704,0.0799,0.0707,0.0400</t>
-  </si>
-  <si>
-    <t>0.6049,0.1215,0.1441,0.1077</t>
-  </si>
-  <si>
-    <t>0.6460,0.0671,0.2672,0.0380</t>
-  </si>
-  <si>
-    <t>0.0489,0.8108,0.6707,0.0053</t>
-  </si>
-  <si>
-    <t>0.6204,0.1190,0.0173,0.0706</t>
-  </si>
-  <si>
-    <t>0.8502,0.1176,0.0070,0.0065</t>
-  </si>
-  <si>
-    <t>0.6050,0.2805,0.0264,0.0160</t>
-  </si>
-  <si>
-    <t>0.5370,0.2511,0.0242,0.0424</t>
-  </si>
-  <si>
-    <t>0.4334,0.3775,0.0194,0.0282</t>
-  </si>
-  <si>
-    <t>0.4203,0.2317,0.0196,0.0782</t>
-  </si>
-  <si>
-    <t>0.8304,0.0676,0.0050,0.0164</t>
-  </si>
-  <si>
-    <t>0.4852,0.1737,0.0120,0.0608</t>
-  </si>
-  <si>
-    <t>0.3797,0.3995,0.3264,0.0334</t>
-  </si>
-  <si>
-    <t>0.8399,0.0574,0.0076,0.0198</t>
-  </si>
-  <si>
-    <t>0.7673,0.1102,0.0206,0.0237</t>
-  </si>
-  <si>
-    <t>0.3916,0.1016,0.5609,0.0161</t>
-  </si>
-  <si>
-    <t>0.1617,0.4246,0.6325,0.0543</t>
-  </si>
-  <si>
-    <t>0.6774,0.1715,0.1261,0.0178</t>
-  </si>
-  <si>
-    <t>0.0872,0.1086,0.9196,0.0008</t>
-  </si>
-  <si>
-    <t>0.5624,0.0723,0.3537,0.0630</t>
-  </si>
-  <si>
-    <t>0.3634,0.2082,0.4485,0.0064</t>
-  </si>
-  <si>
-    <t>0.3588,0.1128,0.5813,0.0125</t>
-  </si>
-  <si>
-    <t>0.4215,0.5128,0.0980,0.0260</t>
-  </si>
-  <si>
-    <t>0.9420,0.0132,0.0130,0.0098</t>
-  </si>
-  <si>
-    <t>0.7640,0.0835,0.1039,0.0482</t>
-  </si>
-  <si>
-    <t>0.8744,0.0284,0.0185,0.0348</t>
-  </si>
-  <si>
-    <t>0.8555,0.0567,0.0072,0.0164</t>
-  </si>
-  <si>
-    <t>0.8601,0.0592,0.0036,0.0094</t>
-  </si>
-  <si>
-    <t>0.5564,0.2299,0.0132,0.0340</t>
-  </si>
-  <si>
-    <t>0.5912,0.1358,0.0246,0.0684</t>
-  </si>
-  <si>
-    <t>0.5238,0.2133,0.0134,0.0312</t>
-  </si>
-  <si>
-    <t>0.7205,0.1036,0.0076,0.0263</t>
-  </si>
-  <si>
-    <t>0.5622,0.2814,0.0198,0.0209</t>
-  </si>
-  <si>
-    <t>0.6485,0.2145,0.0163,0.0205</t>
-  </si>
-  <si>
-    <t>0.6382,0.0771,0.2181,0.0627</t>
-  </si>
-  <si>
-    <t>0.0328,0.5301,0.8978,0.0072</t>
-  </si>
-  <si>
-    <t>0.3191,0.2357,0.5029,0.0554</t>
-  </si>
-  <si>
-    <t>0.7037,0.0734,0.1900,0.0263</t>
-  </si>
-  <si>
-    <t>0.6797,0.0951,0.1537,0.0497</t>
-  </si>
-  <si>
-    <t>0.8054,0.0497,0.0715,0.0490</t>
-  </si>
-  <si>
-    <t>0.8006,0.0612,0.1113,0.0199</t>
-  </si>
-  <si>
-    <t>0.5824,0.2106,0.1983,0.0273</t>
-  </si>
-  <si>
-    <t>0.8033,0.0625,0.0194,0.0473</t>
-  </si>
-  <si>
-    <t>0.5926,0.1544,0.0406,0.1038</t>
-  </si>
-  <si>
-    <t>0.7949,0.0267,0.0265,0.1200</t>
-  </si>
-  <si>
-    <t>0.6664,0.0177,0.0090,0.2808</t>
-  </si>
-  <si>
-    <t>0.7511,0.0142,0.0048,0.1571</t>
-  </si>
-  <si>
-    <t>0.7848,0.0408,0.0159,0.0850</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9528,0.0031,0.0320,0.0075</t>
+  </si>
+  <si>
+    <t>0.0579,0.0011,0.0003,0.9854</t>
+  </si>
+  <si>
+    <t>0.9302,0.0004,0.0002,0.1532</t>
+  </si>
+  <si>
+    <t>0.1677,0.0064,0.0095,0.9169</t>
+  </si>
+  <si>
+    <t>0.9937,0.0030,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0016,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0014,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0017,0.0019,0.0019</t>
+  </si>
+  <si>
+    <t>0.7571,0.0287,0.2440,0.0043</t>
+  </si>
+  <si>
+    <t>0.0879,0.0052,0.9517,0.0005</t>
+  </si>
+  <si>
+    <t>0.2146,0.0202,0.8370,0.0018</t>
+  </si>
+  <si>
+    <t>0.1007,0.0271,0.8585,0.0013</t>
+  </si>
+  <si>
+    <t>0.8884,0.0029,0.1559,0.0022</t>
+  </si>
+  <si>
+    <t>0.0010,0.9972,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.9745,0.0105,0.0034</t>
+  </si>
+  <si>
+    <t>0.0708,0.9140,0.0140,0.0118</t>
+  </si>
+  <si>
+    <t>0.0286,0.9621,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.9954,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.4946,0.0050,0.3814,0.0505</t>
+  </si>
+  <si>
+    <t>0.0771,0.0083,0.8807,0.0211</t>
+  </si>
+  <si>
+    <t>0.0088,0.0026,0.9903,0.0010</t>
+  </si>
+  <si>
+    <t>0.0220,0.0063,0.9710,0.0015</t>
+  </si>
+  <si>
+    <t>0.0141,0.0070,0.9744,0.0031</t>
+  </si>
+  <si>
+    <t>0.1170,0.0080,0.9241,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.0015,0.9914,0.0083</t>
+  </si>
+  <si>
+    <t>0.9421,0.1023,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.3861,0.0596,0.6403,0.0075</t>
+  </si>
+  <si>
+    <t>0.0067,0.0417,0.9894,0.0024</t>
+  </si>
+  <si>
+    <t>0.0066,0.9484,0.1542,0.0016</t>
+  </si>
+  <si>
+    <t>0.9509,0.0126,0.0086,0.0158</t>
+  </si>
+  <si>
+    <t>0.6004,0.0538,0.3869,0.0075</t>
+  </si>
+  <si>
+    <t>0.5365,0.4928,0.0405,0.0031</t>
+  </si>
+  <si>
+    <t>0.0062,0.9704,0.5018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0430,0.9214,0.0281,0.0031</t>
+  </si>
+  <si>
+    <t>0.1346,0.0050,0.8635,0.0083</t>
+  </si>
+  <si>
+    <t>0.0254,0.0326,0.9387,0.0197</t>
+  </si>
+  <si>
+    <t>0.1037,0.0129,0.8943,0.0146</t>
+  </si>
+  <si>
+    <t>0.0049,0.2826,0.9746,0.0034</t>
+  </si>
+  <si>
+    <t>0.0065,0.9824,0.0202,0.0012</t>
+  </si>
+  <si>
+    <t>0.0074,0.0055,0.9816,0.0115</t>
+  </si>
+  <si>
+    <t>0.0103,0.7456,0.0067,0.7373</t>
+  </si>
+  <si>
+    <t>0.0040,0.9699,0.0136,0.0826</t>
+  </si>
+  <si>
+    <t>0.0048,0.9796,0.0750,0.0036</t>
+  </si>
+  <si>
+    <t>0.0019,0.9904,0.0332,0.0081</t>
+  </si>
+  <si>
+    <t>0.0074,0.0399,0.9798,0.0043</t>
+  </si>
+  <si>
+    <t>0.0060,0.8460,0.7627,0.0014</t>
+  </si>
+  <si>
+    <t>0.0051,0.0025,0.9926,0.0003</t>
+  </si>
+  <si>
+    <t>0.0148,0.0022,0.9896,0.0007</t>
+  </si>
+  <si>
+    <t>0.0185,0.0161,0.9779,0.0024</t>
+  </si>
+  <si>
+    <t>0.0333,0.3779,0.6487,0.0006</t>
+  </si>
+  <si>
+    <t>0.9886,0.0096,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9848,0.0032,0.0072,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0010,0.0014,0.0017</t>
+  </si>
+  <si>
+    <t>0.0278,0.0075,0.9730,0.0050</t>
+  </si>
+  <si>
+    <t>0.9886,0.0068,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9965,0.0019,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9823,0.0178,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9041,0.9681,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0530,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.0077,0.9903,0.0014</t>
+  </si>
+  <si>
+    <t>0.0011,0.9179,0.9641,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0031,0.9976,0.0004</t>
+  </si>
+  <si>
+    <t>0.2590,0.6484,0.0447,0.0008</t>
+  </si>
+  <si>
+    <t>0.0181,0.9808,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9440,0.0204,0.0392,0.0047</t>
+  </si>
+  <si>
+    <t>0.0335,0.0570,0.9604,0.0021</t>
+  </si>
+  <si>
+    <t>0.0080,0.0064,0.9888,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9815,0.8851,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9798,0.7914,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9254,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9854,0.9598,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0012,0.0306,0.9774</t>
+  </si>
+  <si>
+    <t>0.0009,0.0025,0.0057,0.9967</t>
+  </si>
+  <si>
+    <t>0.0011,0.0011,0.0012,0.9986</t>
+  </si>
+  <si>
+    <t>0.0133,0.0010,0.0043,0.9908</t>
+  </si>
+  <si>
+    <t>0.0433,0.0150,0.0067,0.9686</t>
+  </si>
+  <si>
+    <t>0.0029,0.0016,0.0205,0.9898</t>
+  </si>
+  <si>
+    <t>0.0003,0.9868,0.8113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9478,0.9453,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.9710,0.3821,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.1802,0.9777,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.9652,0.9835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.9192,0.5397,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0008,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9805,0.0218,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.9939,0.0027,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0031,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9891,0.0105,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9894,0.0044,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.9891,0.0078,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9892,0.0080,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9889,0.0031,0.0059,0.0013</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0054,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9934,0.0029,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0015,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0063,0.0056,0.9853,0.0046</t>
+  </si>
+  <si>
+    <t>0.0143,0.0047,0.9819,0.0016</t>
+  </si>
+  <si>
+    <t>0.9290,0.0057,0.0807,0.0019</t>
+  </si>
+  <si>
+    <t>0.0604,0.0042,0.9560,0.0009</t>
+  </si>
+  <si>
+    <t>0.1037,0.9058,0.0152,0.0007</t>
+  </si>
+  <si>
+    <t>0.0513,0.9388,0.0045,0.0016</t>
+  </si>
+  <si>
+    <t>0.0471,0.9494,0.0049,0.0030</t>
+  </si>
+  <si>
+    <t>0.3120,0.7827,0.0034,0.0021</t>
+  </si>
+  <si>
+    <t>0.0242,0.9729,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.0406,0.9630,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.9144,0.1583,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.3606,0.4157,0.1270,0.0530</t>
+  </si>
+  <si>
+    <t>0.4644,0.0044,0.6998,0.0024</t>
+  </si>
+  <si>
+    <t>0.3790,0.0378,0.5359,0.0412</t>
+  </si>
+  <si>
+    <t>0.4250,0.1003,0.4734,0.0202</t>
+  </si>
+  <si>
+    <t>0.0073,0.1598,0.0060,0.9727</t>
+  </si>
+  <si>
+    <t>0.0053,0.9833,0.0306,0.0052</t>
+  </si>
+  <si>
+    <t>0.0036,0.9821,0.0105,0.0361</t>
+  </si>
+  <si>
+    <t>0.0013,0.9837,0.0115,0.0832</t>
+  </si>
+  <si>
+    <t>0.0018,0.9012,0.9506,0.0007</t>
+  </si>
+  <si>
+    <t>0.0089,0.9859,0.0148,0.0002</t>
+  </si>
+  <si>
+    <t>0.4861,0.6742,0.0069,0.0009</t>
+  </si>
+  <si>
+    <t>0.5063,0.4887,0.0806,0.0049</t>
+  </si>
+  <si>
+    <t>0.9622,0.0226,0.0050,0.0036</t>
+  </si>
+  <si>
+    <t>0.9944,0.0018,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9898,0.0012,0.0016,0.0046</t>
+  </si>
+  <si>
+    <t>0.9676,0.0105,0.0138,0.0031</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.9900,0.0016,0.0042,0.0022</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.8345,0.9841,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.8664,0.8872,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.1525,0.9754,0.0001</t>
+  </si>
+  <si>
+    <t>0.0195,0.0185,0.9653,0.0017</t>
+  </si>
+  <si>
+    <t>0.9502,0.0073,0.0365,0.0013</t>
+  </si>
+  <si>
+    <t>0.9119,0.0105,0.0353,0.0249</t>
+  </si>
+  <si>
+    <t>0.2507,0.0094,0.8225,0.0061</t>
+  </si>
+  <si>
+    <t>0.8697,0.0218,0.0590,0.0236</t>
+  </si>
+  <si>
+    <t>0.1701,0.0008,0.0019,0.9433</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0070,0.9987</t>
+  </si>
+  <si>
+    <t>0.0006,0.0094,0.0020,0.9983</t>
+  </si>
+  <si>
+    <t>0.0116,0.0009,0.0017,0.9940</t>
+  </si>
+  <si>
+    <t>0.0026,0.9367,0.8684,0.0031</t>
+  </si>
+  <si>
+    <t>0.9899,0.0033,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.5889,0.5310,0.0095,0.0043</t>
+  </si>
+  <si>
+    <t>0.9829,0.0025,0.0047,0.0055</t>
+  </si>
+  <si>
+    <t>0.9588,0.0590,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9889,0.0012,0.0012,0.0054</t>
+  </si>
+  <si>
+    <t>0.8148,0.0441,0.0335,0.1411</t>
+  </si>
+  <si>
+    <t>0.9925,0.0013,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.0043,0.2065,0.9805,0.0068</t>
+  </si>
+  <si>
+    <t>0.6111,0.0010,0.0034,0.6137</t>
+  </si>
+  <si>
+    <t>0.9340,0.0126,0.0217,0.0269</t>
+  </si>
+  <si>
+    <t>0.7440,0.2573,0.0129,0.0145</t>
+  </si>
+  <si>
+    <t>0.9300,0.0684,0.0039,0.0031</t>
+  </si>
+  <si>
+    <t>0.9470,0.0270,0.0130,0.0036</t>
+  </si>
+  <si>
+    <t>0.0727,0.8693,0.0835,0.0123</t>
+  </si>
+  <si>
+    <t>0.8767,0.0994,0.0278,0.0075</t>
+  </si>
+  <si>
+    <t>0.9469,0.0269,0.0191,0.0031</t>
+  </si>
+  <si>
+    <t>0.9909,0.0017,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.9911,0.0010,0.0012,0.0050</t>
+  </si>
+  <si>
+    <t>0.9855,0.0032,0.0069,0.0024</t>
+  </si>
+  <si>
+    <t>0.9899,0.0005,0.0006,0.0080</t>
+  </si>
+  <si>
+    <t>0.9837,0.0034,0.0029,0.0051</t>
+  </si>
+  <si>
+    <t>0.9904,0.0017,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.9934,0.0005,0.0012,0.0029</t>
+  </si>
+  <si>
+    <t>0.9961,0.0011,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.8386,0.2501,0.0030,0.0025</t>
+  </si>
+  <si>
+    <t>0.8372,0.2707,0.0037,0.0011</t>
+  </si>
+  <si>
+    <t>0.8791,0.1918,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.0352,0.2112,0.9562,0.0006</t>
+  </si>
+  <si>
+    <t>0.9825,0.0248,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9360,0.0055,0.0679,0.0035</t>
+  </si>
+  <si>
+    <t>0.9866,0.0080,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.9786,0.0198,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.0019,0.0307,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.8472,0.1146,0.0475,0.0026</t>
+  </si>
+  <si>
+    <t>0.0107,0.0051,0.9899,0.0007</t>
+  </si>
+  <si>
+    <t>0.0043,0.0233,0.9885,0.0022</t>
+  </si>
+  <si>
+    <t>0.0070,0.0023,0.9928,0.0004</t>
+  </si>
+  <si>
+    <t>0.0318,0.0118,0.9630,0.0037</t>
+  </si>
+  <si>
+    <t>0.0083,0.0042,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.1040,0.0009,0.9510,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0036,0.9909,0.0023</t>
+  </si>
+  <si>
+    <t>0.0400,0.0179,0.9370,0.0043</t>
+  </si>
+  <si>
+    <t>0.0403,0.1875,0.8642,0.0070</t>
+  </si>
+  <si>
+    <t>0.2604,0.1165,0.5896,0.0260</t>
+  </si>
+  <si>
+    <t>0.1819,0.0310,0.7980,0.0054</t>
+  </si>
+  <si>
+    <t>0.4658,0.2489,0.2172,0.0057</t>
+  </si>
+  <si>
+    <t>0.8452,0.0799,0.0362,0.0025</t>
+  </si>
+  <si>
+    <t>0.1720,0.0132,0.8304,0.0131</t>
+  </si>
+  <si>
+    <t>0.1467,0.0619,0.7879,0.0280</t>
+  </si>
+  <si>
+    <t>0.3489,0.7720,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.3494,0.8166,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8323,0.3255,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9882,0.0113,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9675,0.0447,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.7206,0.1891,0.0680,0.0057</t>
+  </si>
+  <si>
+    <t>0.9785,0.0012,0.0139,0.0012</t>
+  </si>
+  <si>
+    <t>0.8974,0.0207,0.0409,0.0211</t>
+  </si>
+  <si>
+    <t>0.2065,0.0045,0.8651,0.0052</t>
+  </si>
+  <si>
+    <t>0.8707,0.0066,0.1283,0.0055</t>
+  </si>
+  <si>
+    <t>0.0136,0.0174,0.9649,0.0081</t>
+  </si>
+  <si>
+    <t>0.0063,0.1543,0.9701,0.0040</t>
+  </si>
+  <si>
+    <t>0.2342,0.0150,0.8306,0.0046</t>
+  </si>
+  <si>
+    <t>0.0486,0.0831,0.8431,0.0072</t>
+  </si>
+  <si>
+    <t>0.0019,0.6270,0.9419,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0015,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9805,0.0163,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.9925,0.0018,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0035,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9827,0.0127,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9885,0.0061,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9950,0.0020,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0015,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.0839,0.0485,0.8770,0.0098</t>
+  </si>
+  <si>
+    <t>0.7312,0.0756,0.2200,0.0201</t>
+  </si>
+  <si>
+    <t>0.6509,0.0381,0.2815,0.0210</t>
+  </si>
+  <si>
+    <t>0.0080,0.0379,0.9869,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.0088,0.9864,0.0098</t>
+  </si>
+  <si>
+    <t>0.0617,0.0084,0.9472,0.0024</t>
+  </si>
+  <si>
+    <t>0.0007,0.0038,0.9982,0.0005</t>
+  </si>
+  <si>
+    <t>0.0240,0.0578,0.9447,0.0032</t>
+  </si>
+  <si>
+    <t>0.0069,0.0429,0.9842,0.0014</t>
+  </si>
+  <si>
+    <t>0.0085,0.0115,0.9792,0.0021</t>
+  </si>
+  <si>
+    <t>0.0271,0.0214,0.9307,0.0037</t>
+  </si>
+  <si>
+    <t>0.9629,0.0005,0.0491,0.0010</t>
+  </si>
+  <si>
+    <t>0.6174,0.0024,0.4738,0.0049</t>
+  </si>
+  <si>
+    <t>0.6564,0.0140,0.3072,0.0504</t>
+  </si>
+  <si>
+    <t>0.9900,0.0023,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.9916,0.0042,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0014,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9909,0.0058,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0010,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0024,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9832,0.0059,0.0035,0.0041</t>
+  </si>
+  <si>
+    <t>0.9950,0.0011,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0126,0.0951,0.9349,0.0023</t>
+  </si>
+  <si>
+    <t>0.0068,0.0422,0.9847,0.0008</t>
+  </si>
+  <si>
+    <t>0.0103,0.0735,0.9744,0.0017</t>
+  </si>
+  <si>
+    <t>0.0597,0.0094,0.9292,0.0040</t>
+  </si>
+  <si>
+    <t>0.0076,0.0014,0.9895,0.0016</t>
+  </si>
+  <si>
+    <t>0.2631,0.0294,0.6980,0.0631</t>
+  </si>
+  <si>
+    <t>0.0135,0.0244,0.9639,0.0064</t>
+  </si>
+  <si>
+    <t>0.0093,0.0041,0.8795,0.1564</t>
+  </si>
+  <si>
+    <t>0.7088,0.0006,0.0020,0.4807</t>
+  </si>
+  <si>
+    <t>0.0199,0.0046,0.0005,0.9915</t>
+  </si>
+  <si>
+    <t>0.0399,0.0003,0.0044,0.9789</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0006,0.9992</t>
+  </si>
+  <si>
+    <t>0.0008,0.0009,0.0009,0.9989</t>
+  </si>
+  <si>
+    <t>0.6694,0.0074,0.0047,0.4673</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,10 +5134,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
